--- a/Result/profitability/3596.xlsx
+++ b/Result/profitability/3596.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.07375</v>
+        <v>3.12375</v>
       </c>
       <c r="N2" t="n">
-        <v>16.13125</v>
+        <v>16.10125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.59</v>
       </c>
       <c r="M3" t="n">
-        <v>3.025</v>
+        <v>3.09625</v>
       </c>
       <c r="N3" t="n">
-        <v>16.69125</v>
+        <v>16.66875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87125</v>
+        <v>2.90875</v>
       </c>
       <c r="N4" t="n">
-        <v>16.9</v>
+        <v>16.87375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.67</v>
       </c>
       <c r="M5" t="n">
-        <v>2.57</v>
+        <v>2.615</v>
       </c>
       <c r="N5" t="n">
-        <v>16.4575</v>
+        <v>16.475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3575</v>
+        <v>2.3525</v>
       </c>
       <c r="N6" t="n">
-        <v>16.70875</v>
+        <v>16.68875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.1</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0675</v>
+        <v>2.105</v>
       </c>
       <c r="N7" t="n">
-        <v>16.94</v>
+        <v>16.92625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>1.91125</v>
+        <v>1.94375</v>
       </c>
       <c r="N8" t="n">
-        <v>16.7925</v>
+        <v>16.795</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3596</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13882</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11776</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2107</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>929</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>66</v>
+      </c>
+      <c r="J75" t="n">
+        <v>994</v>
+      </c>
+      <c r="K75" t="n">
+        <v>744</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.11125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.2725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2599999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.00131926121372028</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.119205298013245</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1400000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.009308510638297962</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
